--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488003_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488003_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3368</v>
+        <v>1.2684</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4865</v>
+        <v>0.3057</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8504</v>
+        <v>0.9627</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8335</v>
@@ -610,13 +610,13 @@
         <v>0.7929</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1704</v>
+        <v>0.1019</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0696</v>
+        <v>-0.2505</v>
       </c>
       <c r="U2" t="n">
-        <v>0.24</v>
+        <v>0.3523</v>
       </c>
       <c r="V2" t="n">
         <v>1.2071</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BUALO</t>
+          <t>P. FERNANDEZ ANTUNEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0949</v>
+        <v>0.5004</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5035</v>
+        <v>0.4726</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4086</v>
+        <v>0.0278</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.8357</v>
+        <v>0.2444</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7997</v>
+        <v>0.6117</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.6355</v>
+        <v>-0.3673</v>
       </c>
       <c r="J4" t="n">
-        <v>0.679</v>
+        <v>2.6162</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4642</v>
+        <v>1.3992</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.7852</v>
+        <v>1.217</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.5147</v>
+        <v>-2.3718</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6645</v>
+        <v>-0.7875</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8503</v>
+        <v>-1.5843</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
         <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1644</v>
+        <v>-0.3386</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.6847</v>
+        <v>-1.1525</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5203</v>
+        <v>0.8138</v>
       </c>
       <c r="V4" t="n">
-        <v>4.4914</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>4.4914</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ ANTUNEZ</t>
+          <t>A. BUALO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1223</v>
+        <v>0.4921</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1221</v>
+        <v>1.9568</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0002</v>
+        <v>-1.4647</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2444</v>
+        <v>-2.8357</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6117</v>
+        <v>1.7997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3673</v>
+        <v>-4.6355</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6162</v>
+        <v>0.679</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3992</v>
+        <v>3.4642</v>
       </c>
       <c r="L5" t="n">
-        <v>1.217</v>
+        <v>-2.7852</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3718</v>
+        <v>-3.5147</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7875</v>
+        <v>-1.6645</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5843</v>
+        <v>-1.8503</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
         <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9614</v>
+        <v>-0.7672</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.7471</v>
+        <v>-1.2314</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.4642</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.4914</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>4.4914</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8711</v>
+        <v>-0.5259</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4823</v>
+        <v>2.4867</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3888</v>
+        <v>-3.0126</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8939</v>
+        <v>0.189</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.6368</v>
+        <v>-0.1954</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7429</v>
+        <v>0.3844</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7799</v>
+        <v>3.4923</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.6358</v>
+        <v>1.3992</v>
       </c>
       <c r="L6" t="n">
-        <v>1.856</v>
+        <v>2.0931</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1141</v>
+        <v>-3.3033</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.001</v>
+        <v>-1.5946</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.113</v>
+        <v>-1.7087</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9911</v>
+        <v>1.9822</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9911</v>
+        <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0316</v>
+        <v>-0.8865</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2975</v>
+        <v>-1.0056</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2659</v>
+        <v>0.1191</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.944</v>
+        <v>-1.0501</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2371</v>
+        <v>-1.2138</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.1811</v>
+        <v>0.1637</v>
       </c>
       <c r="G7" t="n">
-        <v>0.189</v>
+        <v>-2.175</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1954</v>
+        <v>-2.9114</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3844</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4923</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3992</v>
+        <v>-2.1239</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0931</v>
+        <v>2.0491</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.3033</v>
+        <v>-2.1001</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5946</v>
+        <v>-0.7875</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7087</v>
+        <v>-1.3126</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9822</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3046</v>
+        <v>-0.6332</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2552</v>
+        <v>-1.113</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0494</v>
+        <v>0.4798</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8107</v>
+        <v>2.9474</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.9474</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CABARROCAS MARTIN</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5027</v>
+        <v>-1.1891</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3809</v>
+        <v>-0.9688</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1217</v>
+        <v>-0.2203</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0474</v>
+        <v>-1.8939</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9134</v>
+        <v>-3.6368</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.134</v>
+        <v>1.7429</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1954</v>
+        <v>-0.7799</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3159</v>
+        <v>-2.6358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1205</v>
+        <v>1.856</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.852</v>
+        <v>-1.1141</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5975</v>
+        <v>-1.001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2545</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3465</v>
+        <v>-0.2863</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1944</v>
+        <v>-0.1889</v>
       </c>
       <c r="U8" t="n">
-        <v>0.541</v>
+        <v>-0.0974</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ CAMPOS</t>
+          <t>R. CABARROCAS MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7498</v>
+        <v>-1.7896</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6101</v>
+        <v>-1.4994</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3599</v>
+        <v>-0.2902</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1868</v>
+        <v>-1.0474</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2072</v>
+        <v>-0.9134</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9796</v>
+        <v>-0.134</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7252</v>
+        <v>-0.1954</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1147</v>
+        <v>-0.3159</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.1205</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9119</v>
+        <v>-0.852</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3219</v>
+        <v>-0.5975</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.59</v>
+        <v>-0.2545</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3876</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8006</v>
+        <v>0.0596</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3816</v>
+        <v>-0.3128</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1822</v>
+        <v>0.3725</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.7512</v>
+        <v>-0.6036</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.0178</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>H. FERNANDEZ CAMPOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0493</v>
+        <v>-2.0815</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.848</v>
+        <v>0.5312</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2014</v>
+        <v>-2.6126</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.175</v>
+        <v>-1.1868</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9114</v>
+        <v>-0.2072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7364000000000001</v>
+        <v>-0.9796</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.07480000000000001</v>
+        <v>0.7252</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.1239</v>
+        <v>0.1147</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0491</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1001</v>
+        <v>-1.9119</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7875</v>
+        <v>-0.3219</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3126</v>
+        <v>-1.59</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6324</v>
+        <v>0.4689</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7471</v>
+        <v>-0.4606</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1148</v>
+        <v>0.9295</v>
       </c>
       <c r="V10" t="n">
-        <v>2.9474</v>
+        <v>-2.7512</v>
       </c>
       <c r="W10" t="n">
-        <v>2.9474</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-3.0178</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6718</v>
+        <v>-3.544</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7762</v>
+        <v>-3.2834</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1044</v>
+        <v>-0.2606</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1296</v>
@@ -1312,13 +1312,13 @@
         <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8197</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3103</v>
+        <v>-0.8175</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4906</v>
+        <v>0.1256</v>
       </c>
       <c r="V11" t="n">
         <v>1.2775</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.268599999999999</v>
+        <v>-6.708600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5616</v>
+        <v>-0.001699999999999591</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.706899999999999</v>
+        <v>-6.706799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-12.4578</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.4026</v>
+        <v>-6.402600000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-6.055300000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>4.340500000000001</v>
+        <v>4.3405</v>
       </c>
       <c r="K12" t="n">
         <v>1.880500000000001</v>
@@ -1375,10 +1375,10 @@
         <v>-16.7981</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.283099999999999</v>
+        <v>-8.283100000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.514999999999999</v>
+        <v>-8.515000000000001</v>
       </c>
       <c r="P12" t="n">
         <v>3.9646</v>
@@ -1390,10 +1390,10 @@
         <v>11.8934</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.533399999999999</v>
+        <v>-2.9734</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.092499999999999</v>
+        <v>-6.5328</v>
       </c>
       <c r="U12" t="n">
         <v>3.5594</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.044</v>
+        <v>6.6922</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8772</v>
+        <v>2.3679</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1667</v>
+        <v>4.3244</v>
       </c>
       <c r="G13" t="n">
         <v>4.4044</v>
@@ -1468,13 +1468,13 @@
         <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7603</v>
+        <v>1.4086</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0145</v>
+        <v>-0.5238</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7748</v>
+        <v>1.9324</v>
       </c>
       <c r="V13" t="n">
         <v>0.4828</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. LOPEZ GOMEZ</t>
+          <t>J. LEGANOVIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8514</v>
+        <v>2.6921</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0916</v>
+        <v>3.1741</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7598</v>
+        <v>-0.482</v>
       </c>
       <c r="G14" t="n">
-        <v>1.734</v>
+        <v>1.8671</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2653</v>
+        <v>1.3583</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9993</v>
+        <v>0.5088</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4156</v>
+        <v>2.9776</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0871</v>
+        <v>1.0089</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5027</v>
+        <v>1.9687</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6816</v>
+        <v>-1.1105</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1782</v>
+        <v>0.3494</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5034</v>
+        <v>-1.4599</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8923</v>
+        <v>0.6268</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.756</v>
+        <v>0.1965</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6483</v>
+        <v>0.4303</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8198</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LEGANOVIC</t>
+          <t>P. LOPEZ GOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1795</v>
+        <v>2.5987</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9703</v>
+        <v>2.0916</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7907999999999999</v>
+        <v>0.5071</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8671</v>
+        <v>1.734</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3583</v>
+        <v>-0.2653</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5088</v>
+        <v>1.9993</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9776</v>
+        <v>2.4156</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0089</v>
+        <v>-0.0871</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9687</v>
+        <v>2.5027</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1105</v>
+        <v>-0.6816</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3494</v>
+        <v>-0.1782</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4599</v>
+        <v>-0.5034</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1982</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1142</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0072</v>
+        <v>-0.756</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1215</v>
+        <v>1.3956</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.8198</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="16">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5326</v>
+        <v>1.097</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5122</v>
+        <v>-1.9197</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0448</v>
+        <v>3.0167</v>
       </c>
       <c r="G17" t="n">
         <v>1.5391</v>
@@ -1780,13 +1780,13 @@
         <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>1.244</v>
+        <v>0.8085</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0145</v>
+        <v>-0.422</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2585</v>
+        <v>1.2305</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4577</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4174</v>
+        <v>0.3051</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4037</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.7088</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0863</v>
@@ -1936,13 +1936,13 @@
         <v>0.1982</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0389</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3744</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4133</v>
+        <v>0.301</v>
       </c>
       <c r="V19" t="n">
         <v>0.2666</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>J. VEGA MERAYO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5732</v>
+        <v>-0.4901</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6325</v>
+        <v>0.3771</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0593</v>
+        <v>-0.8671</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8475</v>
+        <v>-0.9706</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2589</v>
+        <v>0.7357</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4114</v>
+        <v>-1.7064</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4906</v>
+        <v>0.8168</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0492</v>
+        <v>0.9218</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5586</v>
+        <v>-0.105</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3569</v>
+        <v>-1.7875</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2096</v>
+        <v>-0.1861</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1472</v>
+        <v>-1.6014</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3876</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
         <v>0.5947</v>
       </c>
       <c r="S20" t="n">
-        <v>0.837</v>
+        <v>0.2735</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8591</v>
+        <v>-0.0522</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0221</v>
+        <v>0.3257</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8701</v>
+        <v>0.6036</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.921</v>
+        <v>-0.8017</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2038</v>
+        <v>-1.1419</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1248</v>
+        <v>0.3401</v>
       </c>
       <c r="G21" t="n">
-        <v>1.726</v>
+        <v>0.8475</v>
       </c>
       <c r="H21" t="n">
-        <v>1.594</v>
+        <v>1.2589</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1319</v>
+        <v>-0.4114</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9509</v>
+        <v>0.4906</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1797</v>
+        <v>1.0492</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7712</v>
+        <v>-0.5586</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2249</v>
+        <v>0.3569</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5857</v>
+        <v>0.2096</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6392</v>
+        <v>0.1472</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4915</v>
+        <v>0.6085</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.756</v>
+        <v>0.3497</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2475</v>
+        <v>0.2587</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.1385</v>
+        <v>-0.8701</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.1385</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VEGA MERAYO</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0275</v>
+        <v>-0.9131</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1323</v>
+        <v>-0.699</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8952</v>
+        <v>-0.2141</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9706</v>
+        <v>2.3679</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7357</v>
+        <v>0.5674</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7064</v>
+        <v>1.8005</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8168</v>
+        <v>1.7786</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9218</v>
+        <v>0.1482</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.105</v>
+        <v>1.6304</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7875</v>
+        <v>0.5893</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1861</v>
+        <v>0.4193</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6014</v>
+        <v>0.17</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3964</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.264</v>
+        <v>0.4432</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5616</v>
+        <v>-0.4954</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2976</v>
+        <v>0.9386</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6036</v>
+        <v>-2.5349</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.5349</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6199</v>
+        <v>-1.051</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0404</v>
+        <v>1.1019</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6603</v>
+        <v>-2.1529</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8309</v>
+        <v>1.726</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4291</v>
+        <v>1.594</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4018</v>
+        <v>0.1319</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0404</v>
+        <v>2.9509</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0404</v>
+        <v>2.1797</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.7712</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8713</v>
+        <v>-1.2249</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4695</v>
+        <v>-0.5857</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4018</v>
+        <v>-0.6392</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1171</v>
+        <v>0.3615</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.8579</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1171</v>
+        <v>1.2194</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8701</v>
+        <v>-3.1385</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8701</v>
+        <v>-3.1385</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0931</v>
+        <v>-1.5919</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.514</v>
+        <v>0.0404</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-1.6322</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3679</v>
+        <v>-0.8309</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5674</v>
+        <v>-0.4291</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8005</v>
+        <v>-0.4018</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7786</v>
+        <v>0.0404</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1482</v>
+        <v>0.0404</v>
       </c>
       <c r="L24" t="n">
-        <v>1.6304</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5893</v>
+        <v>-0.8713</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4193</v>
+        <v>-0.4695</v>
       </c>
       <c r="O24" t="n">
-        <v>0.17</v>
+        <v>-0.4018</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7367</v>
+        <v>-0.089</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3103</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5736</v>
+        <v>-0.089</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.5349</v>
+        <v>-0.8701</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.5349</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.2375</v>
+        <v>-2.9848</v>
       </c>
       <c r="E25" t="n">
         <v>-0.9976</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2399</v>
+        <v>-1.9872</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8562</v>
@@ -2404,13 +2404,13 @@
         <v>0.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7272</v>
+        <v>-0.4744</v>
       </c>
       <c r="T25" t="n">
         <v>-0.624</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1032</v>
+        <v>0.1495</v>
       </c>
       <c r="V25" t="n">
         <v>0.9405</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.268700000000003</v>
+        <v>8.268499999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>6.706999999999998</v>
+        <v>6.707100000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>1.561599999999999</v>
+        <v>1.5616</v>
       </c>
       <c r="G26" t="n">
         <v>12.458</v>
@@ -2458,19 +2458,19 @@
         <v>16.7983</v>
       </c>
       <c r="K26" t="n">
-        <v>8.283099999999999</v>
+        <v>8.283100000000001</v>
       </c>
       <c r="L26" t="n">
         <v>8.5151</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.340400000000001</v>
+        <v>-4.3404</v>
       </c>
       <c r="N26" t="n">
         <v>-1.8803</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.4602</v>
+        <v>-2.460199999999999</v>
       </c>
       <c r="P26" t="n">
         <v>-3.9646</v>
@@ -2479,19 +2479,19 @@
         <v>-11.8932</v>
       </c>
       <c r="R26" t="n">
-        <v>7.9289</v>
+        <v>7.928900000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>4.5332</v>
+        <v>4.533399999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.5594</v>
+        <v>-3.5595</v>
       </c>
       <c r="U26" t="n">
-        <v>8.092700000000002</v>
+        <v>8.092699999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.757999999999999</v>
+        <v>-4.758</v>
       </c>
       <c r="W26" t="n">
         <v>5.3617</v>
